--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_kl_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_kl_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>28-08-2021 08:30</t>
+          <t>2021-08-28 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>05-06-2021 08:30</t>
+          <t>2021-05-06 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>07-08-2021 08:30</t>
+          <t>2021-07-08 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>24-11-2021 08:30</t>
+          <t>2021-11-24 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7649,7 +7649,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>24-05-2021 08:30</t>
+          <t>2021-05-24 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>07-08-2021 08:30</t>
+          <t>2021-07-08 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12565,7 +12565,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>28-08-2021 08:30</t>
+          <t>2021-08-28 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>24-05-2021 08:30</t>
+          <t>2021-05-24 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15767,7 +15767,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18512,7 +18512,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -18884,7 +18884,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19256,7 +19256,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -19909,7 +19909,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>17-07-2021 08:30</t>
+          <t>2021-07-17 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22187,7 +22187,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22466,7 +22466,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22652,7 +22652,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22745,7 +22745,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -22931,7 +22931,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23121,7 +23121,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23501,7 +23501,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>30-07-2021 08:30</t>
+          <t>2021-07-30 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>23-01-2021 08:30</t>
+          <t>2021-01-23 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25300,7 +25300,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25490,7 +25490,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26056,7 +26056,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26428,7 +26428,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26521,7 +26521,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26707,7 +26707,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -26800,7 +26800,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -26986,7 +26986,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27079,7 +27079,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27265,7 +27265,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>23-01-2021 08:30</t>
+          <t>2021-01-23 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27358,7 +27358,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -27451,7 +27451,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>30-03-2021 08:30</t>
+          <t>2021-03-30 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27544,7 +27544,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27637,7 +27637,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27730,7 +27730,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -27823,7 +27823,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -27916,7 +27916,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28009,7 +28009,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28102,7 +28102,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28195,7 +28195,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28288,7 +28288,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28381,7 +28381,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28474,7 +28474,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28567,7 +28567,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28660,7 +28660,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -28753,7 +28753,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -28846,7 +28846,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -28939,7 +28939,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29032,7 +29032,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29125,7 +29125,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="inlineStr"/>
@@ -29218,7 +29218,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29311,7 +29311,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="inlineStr"/>
@@ -29404,7 +29404,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -29497,7 +29497,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -29683,7 +29683,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -29776,7 +29776,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -29869,7 +29869,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30148,7 +30148,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30241,7 +30241,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30334,7 +30334,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30520,7 +30520,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -30706,7 +30706,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -30985,7 +30985,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31078,7 +31078,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31171,7 +31171,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31264,7 +31264,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31357,7 +31357,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31450,7 +31450,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31543,7 +31543,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -31636,7 +31636,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -31729,7 +31729,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -31915,7 +31915,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32008,7 +32008,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32101,7 +32101,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32194,7 +32194,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32473,7 +32473,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32566,7 +32566,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -32659,7 +32659,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -32752,7 +32752,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -32845,7 +32845,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -32938,7 +32938,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33031,7 +33031,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33124,7 +33124,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33217,7 +33217,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33310,7 +33310,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33403,7 +33403,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33496,7 +33496,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -33682,7 +33682,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="inlineStr"/>
@@ -33868,7 +33868,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="inlineStr"/>
@@ -33961,7 +33961,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="inlineStr"/>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="inlineStr"/>
@@ -34147,7 +34147,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="inlineStr"/>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34335,7 +34335,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34525,7 +34525,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -34715,7 +34715,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -34810,7 +34810,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -34905,7 +34905,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35000,7 +35000,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35095,7 +35095,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35285,7 +35285,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="n">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -35665,7 +35665,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="n">
@@ -35855,7 +35855,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>24-06-2021 08:30</t>
+          <t>2021-06-24 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="n">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36045,7 +36045,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36140,7 +36140,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -36235,7 +36235,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -36615,7 +36615,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -36710,7 +36710,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -36805,7 +36805,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37090,7 +37090,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37185,7 +37185,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37280,7 +37280,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37375,7 +37375,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -37470,7 +37470,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -37565,7 +37565,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -37660,7 +37660,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -37753,7 +37753,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -37846,7 +37846,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -37939,7 +37939,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38032,7 +38032,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38125,7 +38125,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
@@ -38218,7 +38218,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="inlineStr"/>
@@ -38311,7 +38311,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="inlineStr"/>
@@ -38404,7 +38404,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="inlineStr"/>
@@ -38497,7 +38497,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -38687,7 +38687,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -38877,7 +38877,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>14-05-2021 08:30</t>
+          <t>2021-05-14 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39067,7 +39067,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39257,7 +39257,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39352,7 +39352,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -39447,7 +39447,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -39637,7 +39637,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -39730,7 +39730,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="inlineStr"/>
@@ -39823,7 +39823,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="inlineStr"/>
@@ -39916,7 +39916,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="inlineStr"/>
@@ -40009,7 +40009,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="inlineStr"/>
@@ -40102,7 +40102,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="inlineStr"/>
@@ -40195,7 +40195,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -40288,7 +40288,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -40381,7 +40381,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -40476,7 +40476,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -40666,7 +40666,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>24-05-2021 08:30</t>
+          <t>2021-05-24 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -40856,7 +40856,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -40951,7 +40951,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41046,7 +41046,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41141,7 +41141,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -41331,7 +41331,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -41521,7 +41521,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -41614,7 +41614,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -41707,7 +41707,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -41800,7 +41800,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -41893,7 +41893,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -41986,7 +41986,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42079,7 +42079,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42174,7 +42174,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -42269,7 +42269,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -42364,7 +42364,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -42459,7 +42459,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -42554,7 +42554,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="n">
@@ -42649,7 +42649,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -42744,7 +42744,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -42839,7 +42839,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -43029,7 +43029,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -43124,7 +43124,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -43219,7 +43219,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -43504,7 +43504,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -43599,7 +43599,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -43789,7 +43789,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -43979,7 +43979,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44074,7 +44074,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44169,7 +44169,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -44264,7 +44264,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -44359,7 +44359,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -44458,7 +44458,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -44559,7 +44559,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -44759,7 +44759,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -44860,7 +44860,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -44959,7 +44959,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45058,7 +45058,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -45157,7 +45157,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="n">
@@ -45256,7 +45256,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="n">
@@ -45355,7 +45355,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="n">
@@ -45454,7 +45454,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="n">
@@ -45553,7 +45553,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="n">
@@ -45654,7 +45654,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="n">
@@ -45755,7 +45755,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="n">
@@ -45854,7 +45854,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="n">
@@ -45953,7 +45953,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="n">
@@ -46054,7 +46054,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="n">
@@ -46153,7 +46153,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="n">
@@ -46252,7 +46252,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="n">
@@ -46351,7 +46351,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="n">
@@ -46450,7 +46450,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="n">
@@ -46549,7 +46549,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="n">
@@ -46650,7 +46650,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="n">
@@ -46751,7 +46751,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="n">
@@ -46850,7 +46850,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="n">
@@ -46949,7 +46949,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="n">
@@ -47050,7 +47050,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47151,7 +47151,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47250,7 +47250,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="n">
@@ -47351,7 +47351,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="n">
@@ -47452,7 +47452,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="n">
@@ -47553,7 +47553,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="n">
@@ -47652,7 +47652,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="n">
@@ -47753,7 +47753,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="n">
@@ -47852,7 +47852,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="n">
@@ -47951,7 +47951,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="n">
@@ -48050,7 +48050,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="n">
@@ -48149,7 +48149,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="n">
@@ -48248,7 +48248,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="n">
@@ -48347,7 +48347,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -48448,7 +48448,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="n">
@@ -48549,7 +48549,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="n">
@@ -48650,7 +48650,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="n">
@@ -48751,7 +48751,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -48850,7 +48850,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -48949,7 +48949,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49050,7 +49050,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49149,7 +49149,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49248,7 +49248,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49347,7 +49347,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -49446,7 +49446,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -49545,7 +49545,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -49646,7 +49646,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -49747,7 +49747,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -49846,7 +49846,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="n">
@@ -49947,7 +49947,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="n">
@@ -50046,7 +50046,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="n">
@@ -50145,7 +50145,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="n">
@@ -50244,7 +50244,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="n">
@@ -50345,7 +50345,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="n">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="n">
@@ -50547,7 +50547,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="n">
@@ -50648,7 +50648,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="n">
@@ -50749,7 +50749,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="n">
@@ -50848,7 +50848,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="n">
@@ -50947,7 +50947,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="n">
@@ -51048,7 +51048,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="n">
@@ -51147,7 +51147,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="n">
@@ -51248,7 +51248,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="n">
